--- a/artfynd/A 49755-2025 artfynd.xlsx
+++ b/artfynd/A 49755-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110679783</v>
+        <v>110679789</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519664.6975840096</v>
+        <v>519699</v>
       </c>
       <c r="R2" t="n">
-        <v>7161156.441739388</v>
+        <v>7161129</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110679781</v>
+        <v>110695382</v>
       </c>
       <c r="B3" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519661.4989926051</v>
+        <v>519726</v>
       </c>
       <c r="R3" t="n">
-        <v>7161185.218232634</v>
+        <v>7161094</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110679784</v>
+        <v>110679782</v>
       </c>
       <c r="B4" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519664.6975840096</v>
+        <v>519663</v>
       </c>
       <c r="R4" t="n">
-        <v>7161156.441739388</v>
+        <v>7161181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110679780</v>
+        <v>110679781</v>
       </c>
       <c r="B5" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519641.5258547543</v>
+        <v>519661</v>
       </c>
       <c r="R5" t="n">
-        <v>7161345.83255514</v>
+        <v>7161185</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110679782</v>
+        <v>110679779</v>
       </c>
       <c r="B6" t="n">
-        <v>93057</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519662.3846648876</v>
+        <v>519616</v>
       </c>
       <c r="R6" t="n">
-        <v>7161181.355699596</v>
+        <v>7161125</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110679789</v>
+        <v>110679785</v>
       </c>
       <c r="B7" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519699.3048104713</v>
+        <v>519696</v>
       </c>
       <c r="R7" t="n">
-        <v>7161128.728038065</v>
+        <v>7161176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1260,7 @@
         <v>110679790</v>
       </c>
       <c r="B8" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519750.0419299144</v>
+        <v>519750</v>
       </c>
       <c r="R8" t="n">
-        <v>7161135.504560741</v>
+        <v>7161136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110679785</v>
+        <v>110695383</v>
       </c>
       <c r="B9" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519695.5557621627</v>
+        <v>519741</v>
       </c>
       <c r="R9" t="n">
-        <v>7161175.982999952</v>
+        <v>7161085</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,15 +1439,403 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110679784</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjuvmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519665</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7161156</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Rasmus Viding</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Rasmus Viding</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110695381</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjuvmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>519726</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7161094</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110679780</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjuvmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>519641</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7161346</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110679783</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjuvmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>519665</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7161156</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
